--- a/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-22T15:25:29+00:00</t>
+    <t>2024-10-26T11:41:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T11:41:35+00:00</t>
+    <t>2024-10-26T12:52:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T12:52:52+00:00</t>
+    <t>2024-10-26T13:45:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T13:45:19+00:00</t>
+    <t>2024-10-26T13:53:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T13:53:56+00:00</t>
+    <t>2024-10-31T15:15:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T15:15:50+00:00</t>
+    <t>2024-11-17T20:36:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T20:36:22+00:00</t>
+    <t>2024-11-17T21:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T21:00:03+00:00</t>
+    <t>2024-11-17T21:23:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T21:23:25+00:00</t>
+    <t>2024-11-27T13:38:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-27T13:38:13+00:00</t>
+    <t>2024-12-15T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-15T13:48:39+00:00</t>
+    <t>2024-12-19T09:41:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-19T09:41:53+00:00</t>
+    <t>2025-01-08T15:19:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-08T15:19:00+00:00</t>
+    <t>2025-01-24T15:25:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T15:25:06+00:00</t>
+    <t>2025-01-27T07:42:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T07:42:42+00:00</t>
+    <t>2025-01-27T10:22:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T10:22:54+00:00</t>
+    <t>2025-01-27T12:06:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-01T11:26:35+00:00</t>
+    <t>2026-08-11T10:57:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-address-additionalInformation</t>
+    <t>https://fhir.hl7.at/core/r4/StructureDefinition/at-core-ext-address-additionalInformation</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T10:57:38+00:00</t>
+    <t>2026-08-11T12:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -135,7 +135,7 @@
     <t>element:Address.line</t>
   </si>
   <si>
-    <t>element:http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-address#Address.line</t>
+    <t>element:https://fhir.hl7.at/core/r4/StructureDefinition/at-core-address#Address.line</t>
   </si>
   <si>
     <t>ID</t>

--- a/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T12:53:53+00:00</t>
+    <t>2026-08-20T09:19:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
